--- a/강의예제/4장_완성한_보고서_공유_및_출력하기/4장_종합문제.xlsx
+++ b/강의예제/4장_완성한_보고서_공유_및_출력하기/4장_종합문제.xlsx
@@ -577,7 +577,7 @@
   ③ 오류 메시지       「수량은 0보다 큰 정수만 입력 가능합니다」          (4-08)
   ④ 글자 숫자 고치기  수량 세 줄을 숫자로                              (1-11)
   ⑤ 단가·금액         INDEX/MATCH 또는 VLOOKUP + IFERROR               (7-04)
-  ⑥ 인쇄 영역·눈금선  견적서 범위만, 눈금선은 끄기                      (4-02)
+  ⑥ 인쇄 영역·눈금선  견적서 범위만, 눈금선은 끄기                      (4-11)
   ⑦ 인쇄 제목         둘째 장에도 머리글이 찍히게                        (4-12)
   ⑧ 최종확인 채우기   [최종확인] 다섯 칸                                —
 ■ 순서를 지켜야 하는 이유
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>4-02</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">

--- a/강의예제/4장_완성한_보고서_공유_및_출력하기/4장_종합문제.xlsx
+++ b/강의예제/4장_완성한_보고서_공유_및_출력하기/4장_종합문제.xlsx
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>단가 = INDEX($M$6:$M$10,MATCH(C6,$K$6:$K$10,0)), 금액 = 수량*단가.</t>
+          <t>F6 = INDEX($M$6:$M$10,MATCH(C6,$K$6:$K$10,0)), G6 = E6*F6 을 G13 까지. 두 줄이 #N/A 인 것을 확인한 뒤 맨 마지막에 =IFERROR(INDEX(…),0) 으로 감쌉니다. 안 감싸면 금액 합계가 #N/A 입니다.</t>
         </is>
       </c>
     </row>
